--- a/Mantenimiento/excels/PIURA-PIURA-PIURA.xlsx
+++ b/Mantenimiento/excels/PIURA-PIURA-PIURA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1524,11 +1424,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1576,11 +1471,6 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1628,11 +1518,6 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1680,11 +1565,6 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1732,11 +1612,6 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1784,11 +1659,6 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1836,11 +1706,6 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1887,11 +1752,6 @@
       </c>
       <c r="K28" t="n">
         <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/PIURA-PIURA-PIURA.xlsx
+++ b/Mantenimiento/excels/PIURA-PIURA-PIURA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>COMPLEJO LA ALBORADA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.18634</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-80.65428</v>
-      </c>
-      <c r="I2" t="n">
-        <v>658</v>
-      </c>
-      <c r="J2" t="n">
-        <v>33</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.18634</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-80.65428</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>PNP BACILIO RAMIREZ PEÑA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.18797</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-80.65006</v>
-      </c>
-      <c r="I3" t="n">
-        <v>860</v>
-      </c>
-      <c r="J3" t="n">
-        <v>40</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.18797</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-80.65006</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>14001 MAGDALENA SEMINARIO DE LLIROD</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.19625</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-80.6379</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1520</v>
-      </c>
-      <c r="J4" t="n">
-        <v>62</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.19625</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-80.6379</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>14007</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.19012</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-80.65418</v>
-      </c>
-      <c r="I5" t="n">
-        <v>804</v>
-      </c>
-      <c r="J5" t="n">
-        <v>34</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.19012</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-80.65418</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>15005</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.2045</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-80.63330000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>390</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.2045</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-80.6333</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>VICTOR FRANCISCO ROSALES ORTEGA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.18607</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-80.63382</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1232</v>
-      </c>
-      <c r="J7" t="n">
-        <v>50</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.18607</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-80.63382</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>FEDERICO HELGUERO SEMINARIO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.174365</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-80.64591299999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1355</v>
-      </c>
-      <c r="J8" t="n">
-        <v>57</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.174365</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-80.645913</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>20436 ROSA SUAREZ RAFAEL</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.183353</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-80.656988</v>
-      </c>
-      <c r="I9" t="n">
-        <v>443</v>
-      </c>
-      <c r="J9" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.183353</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-80.656988</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>20197</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.20372</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-80.63676</v>
-      </c>
-      <c r="I10" t="n">
-        <v>578</v>
-      </c>
-      <c r="J10" t="n">
-        <v>23</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.20372</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-80.63676</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>PARCEMON SALDARRIAGA MONTEJO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.18826</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-80.62914000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>890</v>
-      </c>
-      <c r="J11" t="n">
-        <v>35</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.18826</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-80.62914</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>ANN GOULDEN</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.20277</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-80.62900999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1131</v>
-      </c>
-      <c r="J12" t="n">
-        <v>40</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.20277</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-80.62901</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>IGNACIO MERINO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.17923</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-80.64373999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1290</v>
-      </c>
-      <c r="J13" t="n">
-        <v>51</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.17923</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-80.64374</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>SAN MIGUEL</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.19615</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-80.6349</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3429</v>
-      </c>
-      <c r="J14" t="n">
-        <v>163</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.19615</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-80.6349</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3429</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>CORONEL JOSE JOAQUIN INCLAN</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.19926</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-80.63702000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1080</v>
-      </c>
-      <c r="J15" t="n">
-        <v>43</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.19926</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-80.63702</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>ENRIQUE LOPEZ ALBUJAR</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.19406</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-80.64891</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1064</v>
-      </c>
-      <c r="J16" t="n">
-        <v>69</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.19406</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-80.64891</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>BELEN</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-5.19233</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-80.62737</v>
-      </c>
-      <c r="I17" t="n">
-        <v>982</v>
-      </c>
-      <c r="J17" t="n">
-        <v>50</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.19233</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-80.62737</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>DOMENICO SAVIO</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-5.1819</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-80.63531</v>
-      </c>
-      <c r="I18" t="n">
-        <v>170</v>
-      </c>
-      <c r="J18" t="n">
-        <v>18</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.1819</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-80.63531</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-5.1928</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-80.63403</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J19" t="n">
-        <v>61</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.1928</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-80.63403</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1362,20 +1530,30 @@
           <t>SANTA MARIA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-5.184422</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-80.62765</v>
-      </c>
-      <c r="I20" t="n">
-        <v>847</v>
-      </c>
-      <c r="J20" t="n">
-        <v>45</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.184422</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-80.62765</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1409,20 +1587,30 @@
           <t>TURICARA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-5.169126</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-80.63548900000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>621</v>
-      </c>
-      <c r="J21" t="n">
-        <v>51</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.169126</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-80.635489</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1456,20 +1644,30 @@
           <t>HOGAR SAN ANTONIO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-5.191628</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-80.63440900000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>630</v>
-      </c>
-      <c r="J22" t="n">
-        <v>42</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-5.191628</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-80.634409</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1503,20 +1701,30 @@
           <t>VALLESOL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-5.17874</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-80.6327</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1018</v>
-      </c>
-      <c r="J23" t="n">
-        <v>67</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-5.17874</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-80.6327</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1550,20 +1758,30 @@
           <t>MARIA MONTESSORI</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-5.17481</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-80.6284</v>
-      </c>
-      <c r="I24" t="n">
-        <v>875</v>
-      </c>
-      <c r="J24" t="n">
-        <v>60</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-5.17481</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-80.6284</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1597,20 +1815,30 @@
           <t>LAS PALMAS DE PIURA</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-5.17239</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-80.65609000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>370</v>
-      </c>
-      <c r="J25" t="n">
-        <v>22</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5.17239</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-80.65609</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1644,20 +1872,30 @@
           <t>PROYECTO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-5.18117</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-80.62889</v>
-      </c>
-      <c r="I26" t="n">
-        <v>637</v>
-      </c>
-      <c r="J26" t="n">
-        <v>36</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-5.18117</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-80.62889</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1691,20 +1929,30 @@
           <t>LAS PRADERAS DEL NORTE</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-5.18623</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-80.62975</v>
-      </c>
-      <c r="I27" t="n">
-        <v>268</v>
-      </c>
-      <c r="J27" t="n">
-        <v>10</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5.18623</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-80.62975</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1738,20 +1986,30 @@
           <t>PAUL HARRIS</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-5.18818</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-80.64619</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5.18818</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-80.64619</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
